--- a/data/export/2026-10-27-182路.xlsx
+++ b/data/export/2026-10-27-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,17 +693,17 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -709,13 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>2/12</t>
         </is>
       </c>
     </row>
@@ -743,32 +751,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:33</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,33 +812,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>1/12</t>
         </is>
       </c>
     </row>
@@ -887,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -926,7 +942,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -937,7 +953,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -965,32 +981,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -998,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1022,17 +1042,17 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1042,13 +1062,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>3/12</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1159,7 +1183,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1244,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1294,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1355,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1405,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1389,22 +1413,22 @@
       <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>沪A68870D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>07:28</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1437,12 +1461,12 @@
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1456,7 +1480,7 @@
       <c r="T9" s="2" t="inlineStr"/>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>07:28</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
@@ -1492,7 +1516,677 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:25</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:25</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A32899D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>1/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-27-182路.xlsx
+++ b/data/export/2026-10-27-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:AC23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,14 +708,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>74.0</t>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -773,12 +773,12 @@
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -870,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -903,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -927,17 +931,17 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -947,13 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -991,24 +999,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1018,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -1100,32 +1108,36 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1133,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1157,33 +1169,37 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1283,7 +1299,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1294,7 +1310,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1322,32 +1338,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1355,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1379,33 +1399,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1505,7 +1529,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1516,7 +1540,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1601,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1627,7 +1651,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1712,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1727,7 +1751,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1738,7 +1762,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1823,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1849,7 +1873,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1934,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1960,7 +1984,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2045,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2075,7 +2099,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -2083,22 +2107,22 @@
       <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>沪A31073D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2136,7 +2160,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2150,43 +2174,951 @@
       <c r="T15" s="2" t="inlineStr"/>
       <c r="U15" s="2" t="inlineStr">
         <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>2/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>08:15</t>
         </is>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W15" s="2" t="inlineStr">
+      <c r="W16" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X15" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y15" s="2" t="inlineStr">
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z15" s="2" t="inlineStr">
+      <c r="Z16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>4/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>3/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB15" s="2" t="inlineStr"/>
-      <c r="AC15" s="2" t="inlineStr">
-        <is>
-          <t>—/12</t>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>5/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>5/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-27-182路.xlsx
+++ b/data/export/2026-10-27-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC23"/>
+  <dimension ref="A1:AC28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -1457,32 +1457,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -1490,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1514,17 +1518,17 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
@@ -1534,13 +1538,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -1568,32 +1576,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1601,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1625,33 +1637,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1790,32 +1806,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -1823,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1847,33 +1867,37 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -1901,32 +1925,36 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>07:22</t>
@@ -1934,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1958,33 +1986,37 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -2045,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2084,7 +2116,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2160,7 +2192,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2242,32 +2274,36 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2275,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2299,37 +2335,37 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2426,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2505,7 +2541,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2616,7 +2652,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2670,7 +2706,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -2731,7 +2767,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2842,7 +2878,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2896,7 +2932,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -2957,7 +2993,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3001,13 +3037,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -3015,22 +3055,22 @@
       <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>沪A68870D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -3068,7 +3108,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3112,13 +3152,588 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>8/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB23" s="2" t="inlineStr"/>
-      <c r="AC23" s="2" t="inlineStr">
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
         <is>
           <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A32899D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>10/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>9/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>1/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>5/13</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-27-182路.xlsx
+++ b/data/export/2026-10-27-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC28"/>
+  <dimension ref="A1:AC36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1304,13 +1304,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,17 +1418,17 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1494,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,22 +1537,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1657,12 +1661,12 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1728,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1767,18 +1771,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1882,7 +1890,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1897,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2016,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2121,17 +2129,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2231,7 +2239,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2246,7 +2254,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -2284,24 +2292,24 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2311,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2360,12 +2368,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -2393,32 +2401,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2426,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2450,37 +2462,37 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -2508,32 +2520,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -2541,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2565,33 +2581,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -2619,32 +2639,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2652,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2676,37 +2700,37 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -2734,32 +2758,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>06:22</t>
@@ -2767,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2791,17 +2819,17 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -2811,13 +2839,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -2845,32 +2877,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2878,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2902,32 +2938,32 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -2960,32 +2996,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -2993,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3017,37 +3057,37 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -3075,32 +3115,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3108,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3132,17 +3176,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3152,12 +3196,12 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3190,32 +3234,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3223,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3247,33 +3295,37 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -3334,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3373,7 +3425,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3388,7 +3440,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -3449,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3503,7 +3555,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -3531,32 +3583,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3564,7 +3620,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3588,17 +3644,17 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -3608,17 +3664,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -3626,22 +3682,22 @@
       <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>沪A31073D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3679,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3693,47 +3749,967 @@
       <c r="T28" s="2" t="inlineStr"/>
       <c r="U28" s="2" t="inlineStr">
         <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>4/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
           <t>10:15</t>
         </is>
       </c>
-      <c r="V28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W28" s="2" t="inlineStr">
+      <c r="W29" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X28" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y28" s="2" t="inlineStr">
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z28" s="2" t="inlineStr">
+      <c r="Z29" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
+      <c r="AA29" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB28" s="2" t="inlineStr">
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>83.5</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>8/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>10/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>7/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
         <is>
           <t>85.0</t>
         </is>
       </c>
-      <c r="AC28" s="2" t="inlineStr">
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>6/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>79.5</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
         <is>
           <t>5/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>3/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A32899D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>13/13</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-27-182路.xlsx
+++ b/data/export/2026-10-27-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC36"/>
+  <dimension ref="A1:AC41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1895,12 +1895,12 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2009,17 +2009,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2358,22 +2358,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2482,17 +2482,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,22 +2715,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -3353,32 +3353,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -3386,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3410,17 +3414,17 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -3430,12 +3434,12 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3468,32 +3472,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>07:22</t>
@@ -3501,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3525,32 +3533,32 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3593,24 +3601,24 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3620,7 +3628,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3659,7 +3667,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3669,12 +3677,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -3702,32 +3710,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3735,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3759,17 +3771,17 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -3779,7 +3791,7 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
@@ -3817,32 +3829,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3850,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3874,37 +3890,37 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -3932,32 +3948,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3965,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3989,17 +4009,17 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -4009,17 +4029,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4119,7 +4139,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4134,7 +4154,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -4162,32 +4182,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4195,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4219,37 +4243,37 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4364,7 +4388,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4479,7 +4503,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4564,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4594,7 +4618,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4679,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4699,17 +4723,592 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>13/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>3/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>12/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>78.3</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>5/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB36" s="2" t="inlineStr">
-        <is>
-          <t>97.0</t>
-        </is>
-      </c>
-      <c r="AC36" s="2" t="inlineStr">
-        <is>
-          <t>13/13</t>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>10/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>7/13</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-27-182路.xlsx
+++ b/data/export/2026-10-27-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC41"/>
+  <dimension ref="A1:AC47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,12 +832,12 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1537,22 +1537,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,14 +1656,14 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
           <t>83.5</t>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,22 +1890,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2477,22 +2477,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2601,17 +2601,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2725,12 +2725,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3072,22 +3072,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3191,14 +3191,14 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>83.5</t>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3429,22 +3429,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -3958,24 +3958,24 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4024,22 +4024,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -4067,32 +4067,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -4100,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4124,17 +4128,17 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4144,17 +4148,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -4192,24 +4196,24 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -4219,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4268,12 +4272,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -4301,32 +4305,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4334,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4358,17 +4366,17 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
@@ -4378,17 +4386,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -4416,32 +4424,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -4449,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4473,37 +4485,37 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -4531,32 +4543,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4564,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4588,17 +4604,17 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4608,7 +4624,7 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
@@ -4646,32 +4662,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -4679,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4703,37 +4723,37 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -4761,32 +4781,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4794,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4818,17 +4842,17 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -4838,12 +4862,12 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4909,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4948,7 +4972,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4963,7 +4987,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -5024,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5078,7 +5102,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -5139,7 +5163,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5183,17 +5207,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5303,12 +5327,702 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>75.7</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>5/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>83.5</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>12/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A32899D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
           <t>80.0</t>
         </is>
       </c>
-      <c r="AC41" s="2" t="inlineStr">
-        <is>
-          <t>7/13</t>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>9/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>4/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>13/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>80.7</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>10/13</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-27-182路.xlsx
+++ b/data/export/2026-10-27-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC47"/>
+  <dimension ref="A1:AC51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,14 +1418,14 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
           <t>78.3</t>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,22 +1656,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2014,17 +2014,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2363,12 +2363,12 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,22 +2596,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2720,17 +2720,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2953,14 +2953,14 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
           <t>78.3</t>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3077,12 +3077,12 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3191,22 +3191,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3553,17 +3553,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3677,12 +3677,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4143,22 +4143,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4267,17 +4267,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4381,14 +4381,14 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
           <t>78.3</t>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4505,12 +4505,12 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -4791,24 +4791,24 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -4900,32 +4900,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>07:22</t>
@@ -4933,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4957,17 +4961,17 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4977,17 +4981,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -5015,32 +5019,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5048,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5072,17 +5080,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5092,12 +5100,12 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5130,32 +5138,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -5163,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5187,37 +5199,37 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -5245,32 +5257,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>66分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5278,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5302,17 +5318,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5322,17 +5338,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -5360,32 +5376,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -5393,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5417,17 +5437,17 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5437,12 +5457,12 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5475,32 +5495,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5508,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5532,37 +5556,37 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5677,7 +5701,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5853,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5897,17 +5921,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -5968,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6022,7 +6046,467 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>13/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>5/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>78.3</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>9/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>2/13</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-27-182路.xlsx
+++ b/data/export/2026-10-27-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC51"/>
+  <dimension ref="A1:AC56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1666,12 +1666,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1895,17 +1895,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2014,17 +2014,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2239,17 +2239,17 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2477,22 +2477,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3434,17 +3434,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3553,17 +3553,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3786,17 +3786,17 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4024,22 +4024,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4743,17 +4743,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4981,17 +4981,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5505,24 +5505,24 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5581,12 +5581,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -5614,32 +5614,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -5647,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5671,17 +5675,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5691,17 +5695,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -5729,32 +5733,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5762,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5786,32 +5794,32 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5844,32 +5852,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>07:22</t>
@@ -5877,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5901,17 +5913,17 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5921,17 +5933,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -5959,32 +5971,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5992,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6016,37 +6032,37 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -6107,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6222,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6261,7 +6277,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6276,7 +6292,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -6337,7 +6353,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6386,12 +6402,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -6452,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6510,6 +6526,581 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>72.7</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>4/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>1/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>12/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>2/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>78.3</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-27-182路.xlsx
+++ b/data/export/2026-10-27-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC56"/>
+  <dimension ref="A1:AC61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,14 +946,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
           <t>76.8</t>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,14 +1184,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
           <t>77.2</t>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,17 +1299,17 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1537,14 +1537,14 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
           <t>75.0</t>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1661,17 +1661,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,22 +1771,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2358,14 +2358,14 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
           <t>76.8</t>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,14 +2715,14 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
           <t>77.2</t>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2834,17 +2834,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3072,14 +3072,14 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
           <t>75.0</t>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3196,17 +3196,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3310,22 +3310,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3558,12 +3558,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3905,14 +3905,14 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
           <t>76.8</t>
@@ -3920,7 +3920,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4034,12 +4034,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4148,12 +4148,12 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4262,14 +4262,14 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
           <t>77.2</t>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4386,17 +4386,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4500,14 +4500,14 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
           <t>75.0</t>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4619,22 +4619,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5095,14 +5095,14 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
           <t>76.8</t>
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5333,14 +5333,14 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
           <t>77.2</t>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5452,14 +5452,14 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
           <t>75.0</t>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5576,17 +5576,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -5705,7 +5705,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5814,12 +5814,12 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5862,12 +5862,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -5981,24 +5981,24 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -6008,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6057,12 +6057,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -6090,32 +6090,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -6123,7 +6127,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6147,17 +6151,17 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6167,12 +6171,12 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6205,32 +6209,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6238,7 +6246,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6262,17 +6270,17 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
@@ -6282,17 +6290,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -6320,32 +6328,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6353,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6377,17 +6389,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6397,17 +6409,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -6435,32 +6447,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6468,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6492,37 +6508,37 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -6550,32 +6566,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6583,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6607,17 +6627,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6627,12 +6647,12 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6665,32 +6685,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>66分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:22</t>
@@ -6698,7 +6722,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6722,32 +6746,32 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6813,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6862,12 +6886,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -6928,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7043,7 +7067,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7087,17 +7111,592 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>75.5</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>7/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>77.2</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>9/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>76.8</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>8/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB56" s="2" t="inlineStr">
-        <is>
-          <t>78.3</t>
-        </is>
-      </c>
-      <c r="AC56" s="2" t="inlineStr">
-        <is>
-          <t>11/13</t>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>72.3</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>3/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>6/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>1/13</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-27-182路.xlsx
+++ b/data/export/2026-10-27-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC61"/>
+  <dimension ref="A1:AC63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1781,12 +1781,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2482,17 +2482,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3429,7 +3429,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4029,17 +4029,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -6008,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6052,17 +6052,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -6457,24 +6457,24 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6484,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6533,12 +6533,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6695,12 +6695,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>66分钟</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6804,32 +6804,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6837,7 +6841,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6861,17 +6865,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6881,17 +6885,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6956,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6991,7 +6995,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -7006,7 +7010,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -7067,7 +7071,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7182,7 +7186,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7297,7 +7301,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7412,7 +7416,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7461,12 +7465,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7531,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7642,7 +7646,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7691,12 +7695,242 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
           <t>1/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A32899D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>3/13</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-27-182路.xlsx
+++ b/data/export/2026-10-27-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC63"/>
+  <dimension ref="A1:AC68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2129,17 +2129,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,22 +2715,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3672,17 +3672,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4262,22 +4262,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4386,17 +4386,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4862,17 +4862,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5333,22 +5333,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5809,7 +5809,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -6008,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6290,17 +6290,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6484,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6538,7 +6538,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -6588,12 +6588,12 @@
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6695,24 +6695,24 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>67分钟</t>
+          <t>66分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6923,32 +6923,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6956,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6980,17 +6984,17 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
@@ -7000,17 +7004,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -7038,32 +7042,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7071,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7095,17 +7103,17 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -7115,17 +7123,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -7153,32 +7161,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7186,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7210,37 +7222,37 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -7301,7 +7313,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7340,7 +7352,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7355,7 +7367,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -7416,7 +7428,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7470,7 +7482,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -7488,7 +7500,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -7531,7 +7543,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7545,7 +7557,7 @@
       <c r="T60" s="2" t="inlineStr"/>
       <c r="U60" s="2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="V60" s="2" t="inlineStr">
@@ -7646,7 +7658,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7695,7 +7707,7 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7761,7 +7773,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7823,22 +7835,22 @@
       <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>沪A66513D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>16:35</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -7876,7 +7888,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7890,47 +7902,622 @@
       <c r="T63" s="2" t="inlineStr"/>
       <c r="U63" s="2" t="inlineStr">
         <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>79.2</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>13/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
           <t>16:35</t>
         </is>
       </c>
-      <c r="V63" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W63" s="2" t="inlineStr">
+      <c r="W64" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X63" s="2" t="inlineStr">
+      <c r="X64" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y63" s="2" t="inlineStr">
+      <c r="Y64" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z63" s="2" t="inlineStr">
+      <c r="Z64" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB63" s="2" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
-      <c r="AC63" s="2" t="inlineStr">
-        <is>
-          <t>3/13</t>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>2/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>73.5</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>4/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>77.8</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>10/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>76.2</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>7/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>76.8</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>9/13</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-27-182路.xlsx
+++ b/data/export/2026-10-27-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC68"/>
+  <dimension ref="A1:AC76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,14 +1065,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
           <t>78.4</t>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,22 +1418,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1537,22 +1537,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,17 +1656,17 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,22 +1771,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,22 +1890,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2363,17 +2363,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2477,14 +2477,14 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
           <t>78.4</t>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,14 +2596,14 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
           <t>73.8</t>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2953,22 +2953,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3072,22 +3072,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3191,17 +3191,17 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3310,22 +3310,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3429,22 +3429,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3667,22 +3667,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3910,17 +3910,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4024,14 +4024,14 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
           <t>78.4</t>
@@ -4039,7 +4039,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4143,14 +4143,14 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
           <t>73.8</t>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4381,22 +4381,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4500,22 +4500,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4619,22 +4619,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4738,22 +4738,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4857,22 +4857,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5100,17 +5100,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5214,14 +5214,14 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
           <t>73.8</t>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5452,22 +5452,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5571,17 +5571,17 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5690,22 +5690,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6047,14 +6047,14 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
           <t>78.4</t>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6166,14 +6166,14 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
           <t>73.8</t>
@@ -6181,7 +6181,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6285,22 +6285,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6404,17 +6404,17 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6484,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6523,22 +6523,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6766,12 +6766,12 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6880,14 +6880,14 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
           <t>78.4</t>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6999,22 +6999,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -7052,24 +7052,24 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7118,22 +7118,22 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -7171,12 +7171,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7247,7 +7247,7 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7280,32 +7280,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7313,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7337,17 +7341,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7357,17 +7361,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -7395,32 +7399,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7428,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7452,37 +7460,37 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -7510,32 +7518,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -7543,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7567,37 +7579,37 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -7625,32 +7637,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>06:22</t>
@@ -7658,7 +7674,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7682,17 +7698,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7702,12 +7718,12 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7740,32 +7756,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -7773,7 +7793,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7797,37 +7817,37 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -7855,32 +7875,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7888,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7912,32 +7936,32 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -7970,32 +7994,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8003,7 +8031,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8027,37 +8055,37 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -8118,7 +8146,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8172,7 +8200,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -8233,7 +8261,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8287,7 +8315,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -8348,7 +8376,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8397,7 +8425,7 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8410,22 +8438,22 @@
       <c r="A68" s="2" t="inlineStr"/>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>沪A31073D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -8463,7 +8491,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8477,47 +8505,967 @@
       <c r="T68" s="2" t="inlineStr"/>
       <c r="U68" s="2" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>78.4</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="V68" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W68" s="2" t="inlineStr">
+      <c r="W69" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X68" s="2" t="inlineStr">
+      <c r="X69" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y68" s="2" t="inlineStr">
+      <c r="Y69" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z68" s="2" t="inlineStr">
+      <c r="Z69" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>76.6</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>8/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB68" s="2" t="inlineStr">
-        <is>
-          <t>76.8</t>
-        </is>
-      </c>
-      <c r="AC68" s="2" t="inlineStr">
-        <is>
-          <t>9/13</t>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>4/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>74.4</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>5/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A32899D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>12/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>77.8</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>10/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>13/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>73.5</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>2/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>74.4</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>5/13</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-27-182路.xlsx
+++ b/data/export/2026-10-27-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC76"/>
+  <dimension ref="A1:AC82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2239,22 +2239,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2363,17 +2363,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,22 +2715,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3677,12 +3677,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3786,22 +3786,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3910,17 +3910,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4262,22 +4262,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5100,17 +5100,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5333,22 +5333,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5452,7 +5452,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5809,22 +5809,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6484,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6642,22 +6642,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6880,7 +6880,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7009,12 +7009,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7133,7 +7133,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7237,22 +7237,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7361,17 +7361,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7766,24 +7766,24 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7897,12 +7897,12 @@
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7912,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8004,24 +8004,24 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -8113,32 +8113,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8146,7 +8150,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8170,37 +8174,37 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -8261,7 +8265,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8300,7 +8304,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8315,7 +8319,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -8343,32 +8347,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8376,7 +8384,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8400,37 +8408,37 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8499,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8530,7 +8538,7 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
@@ -8545,7 +8553,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -8573,32 +8581,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8606,7 +8618,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8630,17 +8642,17 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
@@ -8650,17 +8662,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -8721,7 +8733,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8760,7 +8772,7 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -8775,7 +8787,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -8836,7 +8848,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8875,7 +8887,7 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
@@ -8951,7 +8963,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9000,7 +9012,7 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
@@ -9066,7 +9078,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9120,7 +9132,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -9181,7 +9193,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9243,22 +9255,22 @@
       <c r="A75" s="2" t="inlineStr"/>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>沪A68870D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -9296,7 +9308,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9335,22 +9347,22 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -9358,7 +9370,7 @@
       <c r="A76" s="2" t="inlineStr"/>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>沪A66513D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -9368,7 +9380,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -9411,7 +9423,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9425,45 +9437,735 @@
       <c r="T76" s="2" t="inlineStr"/>
       <c r="U76" s="2" t="inlineStr">
         <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>73.5</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>2/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>77.8</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>7/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
           <t>18:40</t>
         </is>
       </c>
-      <c r="V76" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W76" s="2" t="inlineStr">
+      <c r="W78" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X76" s="2" t="inlineStr">
+      <c r="X78" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y76" s="2" t="inlineStr">
+      <c r="Y78" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z76" s="2" t="inlineStr">
+      <c r="Z78" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA76" s="2" t="inlineStr">
+      <c r="AA78" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB76" s="2" t="inlineStr">
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>4/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>78.4</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>10/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>9/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>19:08</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>19:08</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>3/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
         <is>
           <t>74.4</t>
         </is>
       </c>
-      <c r="AC76" s="2" t="inlineStr">
+      <c r="AC82" s="2" t="inlineStr">
         <is>
           <t>5/13</t>
         </is>

--- a/data/export/2026-10-27-182路.xlsx
+++ b/data/export/2026-10-27-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC82"/>
+  <dimension ref="A1:AC86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,22 +1418,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,17 +1890,17 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2244,17 +2244,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2601,17 +2601,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2725,12 +2725,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2953,22 +2953,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3077,12 +3077,12 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3429,17 +3429,17 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3791,17 +3791,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4148,17 +4148,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4381,22 +4381,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4505,12 +4505,12 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4738,17 +4738,17 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5219,17 +5219,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5343,12 +5343,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5690,17 +5690,17 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5814,17 +5814,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6171,17 +6171,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6285,22 +6285,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6484,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6647,17 +6647,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6999,7 +6999,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7118,22 +7118,22 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7247,12 +7247,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7475,7 +7475,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7599,12 +7599,12 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7832,17 +7832,17 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7912,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -8150,7 +8150,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8194,17 +8194,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -8265,7 +8265,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8319,7 +8319,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -8357,24 +8357,24 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8384,7 +8384,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8433,12 +8433,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -8499,7 +8499,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -8603,12 +8603,12 @@
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8618,7 +8618,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8672,7 +8672,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -8700,32 +8700,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -8733,7 +8737,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8757,17 +8761,17 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
@@ -8777,17 +8781,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -8815,32 +8819,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -8848,7 +8856,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8872,17 +8880,17 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
@@ -8892,12 +8900,12 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -8930,32 +8938,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -8963,7 +8975,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8987,32 +8999,32 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
@@ -9045,32 +9057,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9078,7 +9094,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9102,37 +9118,37 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -9160,32 +9176,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9193,7 +9213,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9217,17 +9237,17 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
@@ -9237,12 +9257,12 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9275,32 +9295,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9308,7 +9332,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9332,17 +9356,17 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
@@ -9352,17 +9376,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -9423,7 +9447,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9462,7 +9486,7 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9538,7 +9562,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9592,7 +9616,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -9653,7 +9677,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9692,7 +9716,7 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9707,7 +9731,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -9768,7 +9792,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9822,7 +9846,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -9883,7 +9907,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9932,12 +9956,12 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -9998,7 +10022,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10042,17 +10066,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -10060,22 +10084,22 @@
       <c r="A82" s="2" t="inlineStr"/>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>沪A55712D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -10108,12 +10132,12 @@
       <c r="M82" s="2" t="inlineStr"/>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10157,17 +10181,477 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>78.7</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>10/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>76.7</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>5/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>73.5</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>2/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A32899D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>12/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB82" s="2" t="inlineStr">
-        <is>
-          <t>74.4</t>
-        </is>
-      </c>
-      <c r="AC82" s="2" t="inlineStr">
-        <is>
-          <t>5/13</t>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>3/13</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-27-182路.xlsx
+++ b/data/export/2026-10-27-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC86"/>
+  <dimension ref="A1:AC89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1537,22 +1537,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1776,17 +1776,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2014,17 +2014,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2129,17 +2129,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2482,17 +2482,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2601,17 +2601,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,22 +2715,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3072,22 +3072,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3315,17 +3315,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3429,7 +3429,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3553,17 +3553,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3672,17 +3672,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4029,17 +4029,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4148,17 +4148,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4262,22 +4262,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4500,22 +4500,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4624,17 +4624,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4862,17 +4862,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4981,17 +4981,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5219,17 +5219,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5333,22 +5333,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5452,22 +5452,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5933,17 +5933,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6052,17 +6052,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6171,17 +6171,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6290,7 +6290,7 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6528,17 +6528,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6885,17 +6885,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7004,17 +7004,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
@@ -7133,7 +7133,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7237,22 +7237,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -7371,7 +7371,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7480,17 +7480,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -7555,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7594,22 +7594,22 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7832,7 +7832,7 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8075,17 +8075,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -8150,7 +8150,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8265,7 +8265,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8309,17 +8309,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -8384,7 +8384,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8423,22 +8423,22 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -8499,7 +8499,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8543,17 +8543,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -8672,7 +8672,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -8737,7 +8737,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8781,17 +8781,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -8856,7 +8856,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8895,22 +8895,22 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9014,7 +9014,7 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
@@ -9094,7 +9094,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -9332,7 +9332,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9414,32 +9414,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9447,7 +9451,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9471,17 +9475,17 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
@@ -9491,17 +9495,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -9529,32 +9533,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>07:22</t>
@@ -9562,7 +9570,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9586,17 +9594,17 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
@@ -9606,17 +9614,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -9644,32 +9652,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9677,7 +9689,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9701,17 +9713,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9721,17 +9733,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -9759,32 +9771,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9792,7 +9808,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9816,17 +9832,17 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
@@ -9836,17 +9852,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -9874,32 +9890,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9907,7 +9927,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9931,37 +9951,37 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA80" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -9989,32 +10009,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -10022,7 +10046,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10046,17 +10070,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10066,17 +10090,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -10104,32 +10128,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10137,7 +10165,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10161,17 +10189,17 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
@@ -10181,7 +10209,7 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
@@ -10191,7 +10219,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -10219,32 +10247,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -10252,7 +10284,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10276,37 +10308,37 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA83" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -10367,7 +10399,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10411,17 +10443,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -10482,7 +10514,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10521,7 +10553,7 @@
       </c>
       <c r="Z85" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA85" s="2" t="inlineStr">
@@ -10597,7 +10629,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10641,17 +10673,362 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>2/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>77.3</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>6/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>76.1</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>4/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A32899D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>12/13</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-27-182路.xlsx
+++ b/data/export/2026-10-27-182路.xlsx
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,12 +832,12 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1895,12 +1895,12 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4267,12 +4267,12 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4624,12 +4624,12 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5695,12 +5695,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6484,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7242,12 +7242,12 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7837,12 +7837,12 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8384,7 +8384,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8428,12 +8428,12 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -8856,7 +8856,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9019,12 +9019,12 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
@@ -9094,7 +9094,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9451,7 +9451,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9495,12 +9495,12 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9689,7 +9689,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9733,12 +9733,12 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9971,12 +9971,12 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -10165,7 +10165,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10257,19 +10257,19 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
@@ -10284,7 +10284,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10333,12 +10333,12 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -10366,32 +10366,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10399,7 +10403,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10423,17 +10427,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10443,12 +10447,12 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
@@ -10481,32 +10485,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -10514,7 +10522,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10538,17 +10546,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10558,12 +10566,12 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
@@ -10596,32 +10604,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10629,7 +10641,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10653,17 +10665,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10673,12 +10685,12 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
@@ -10711,32 +10723,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:49</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10744,7 +10760,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10768,17 +10784,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10788,12 +10804,12 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
@@ -10859,7 +10875,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10908,12 +10924,12 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -10974,7 +10990,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11018,12 +11034,12 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">

--- a/data/export/2026-10-27-182路.xlsx
+++ b/data/export/2026-10-27-182路.xlsx
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1542,17 +1542,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3077,17 +3077,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4505,17 +4505,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5457,17 +5457,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7247,7 +7247,7 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7599,17 +7599,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -8384,7 +8384,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8433,7 +8433,7 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -8856,7 +8856,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8900,17 +8900,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9976,7 +9976,7 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -10284,7 +10284,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10328,17 +10328,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -10522,7 +10522,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10733,24 +10733,24 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>21:49</t>
+          <t>21:44</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -10760,7 +10760,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10809,7 +10809,7 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
@@ -10842,32 +10842,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -10875,7 +10879,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10899,17 +10903,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10919,17 +10923,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -10990,7 +10994,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
